--- a/output/roomself_excel/11375.xlsx
+++ b/output/roomself_excel/11375.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>185166</v>
+        <v>114235</v>
       </c>
       <c r="D2" t="n">
-        <v>3468</v>
+        <v>2704</v>
       </c>
       <c r="E2" t="n">
-        <v>529</v>
+        <v>384</v>
       </c>
       <c r="F2" t="n">
-        <v>418</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>118461</v>
+        <v>185166</v>
       </c>
       <c r="D3" t="n">
-        <v>3988</v>
+        <v>3468</v>
       </c>
       <c r="E3" t="n">
-        <v>1018</v>
+        <v>529</v>
       </c>
       <c r="F3" t="n">
-        <v>894</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>114235</v>
+        <v>119253</v>
       </c>
       <c r="D4" t="n">
-        <v>2704</v>
+        <v>2776</v>
       </c>
       <c r="E4" t="n">
-        <v>894</v>
+        <v>418</v>
       </c>
       <c r="F4" t="n">
-        <v>372</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>70490</v>
+        <v>17061</v>
       </c>
       <c r="D5" t="n">
-        <v>2268</v>
+        <v>1132</v>
       </c>
       <c r="E5" t="n">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>108928</v>
+        <v>14895</v>
       </c>
       <c r="D6" t="n">
-        <v>4156</v>
+        <v>1120</v>
       </c>
       <c r="E6" t="n">
-        <v>614</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>66946</v>
+        <v>48495</v>
       </c>
       <c r="D7" t="n">
-        <v>2180</v>
+        <v>1792</v>
       </c>
       <c r="E7" t="n">
-        <v>358</v>
+        <v>302</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>76450</v>
+        <v>118461</v>
       </c>
       <c r="D8" t="n">
-        <v>2544</v>
+        <v>3988</v>
       </c>
       <c r="E8" t="n">
-        <v>455</v>
+        <v>894</v>
       </c>
       <c r="F8" t="n">
-        <v>432</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>120928</v>
+        <v>108928</v>
       </c>
       <c r="D9" t="n">
-        <v>3080</v>
+        <v>4156</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17061</v>
+        <v>19592</v>
       </c>
       <c r="D10" t="n">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E10" t="n">
-        <v>402</v>
+        <v>124</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>32025</v>
+        <v>70490</v>
       </c>
       <c r="D11" t="n">
-        <v>1432</v>
+        <v>2268</v>
       </c>
       <c r="E11" t="n">
-        <v>175</v>
+        <v>415</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>135216</v>
+        <v>66946</v>
       </c>
       <c r="D12" t="n">
-        <v>3164</v>
+        <v>2180</v>
       </c>
       <c r="E12" t="n">
-        <v>433</v>
+        <v>358</v>
       </c>
       <c r="F12" t="n">
-        <v>369</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14895</v>
+        <v>50382</v>
       </c>
       <c r="D13" t="n">
-        <v>1120</v>
+        <v>2028</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>119253</v>
+        <v>48750</v>
       </c>
       <c r="D14" t="n">
-        <v>2776</v>
+        <v>2020</v>
       </c>
       <c r="E14" t="n">
-        <v>418</v>
+        <v>375</v>
       </c>
       <c r="F14" t="n">
-        <v>350</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>50382</v>
+        <v>172914</v>
       </c>
       <c r="D15" t="n">
-        <v>2028</v>
+        <v>3372</v>
       </c>
       <c r="E15" t="n">
-        <v>446</v>
+        <v>696</v>
       </c>
       <c r="F15" t="n">
-        <v>317</v>
+        <v>385</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>48495</v>
+        <v>121344</v>
       </c>
       <c r="D16" t="n">
-        <v>1792</v>
+        <v>2800</v>
       </c>
       <c r="E16" t="n">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="F16" t="n">
-        <v>220</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23711</v>
+        <v>282564</v>
       </c>
       <c r="D17" t="n">
-        <v>1248</v>
+        <v>5012</v>
       </c>
       <c r="E17" t="n">
-        <v>181</v>
+        <v>614</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>527</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>48750</v>
+        <v>76450</v>
       </c>
       <c r="D18" t="n">
-        <v>2020</v>
+        <v>2544</v>
       </c>
       <c r="E18" t="n">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19592</v>
+        <v>120928</v>
       </c>
       <c r="D19" t="n">
-        <v>1128</v>
+        <v>3080</v>
       </c>
       <c r="E19" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>282564</v>
+        <v>32025</v>
       </c>
       <c r="D20" t="n">
-        <v>5012</v>
+        <v>1432</v>
       </c>
       <c r="E20" t="n">
-        <v>1021</v>
+        <v>175</v>
       </c>
       <c r="F20" t="n">
-        <v>527</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
@@ -884,20 +884,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>172914</v>
+        <v>135216</v>
       </c>
       <c r="D21" t="n">
-        <v>3372</v>
+        <v>3164</v>
       </c>
       <c r="E21" t="n">
-        <v>696</v>
+        <v>433</v>
       </c>
       <c r="F21" t="n">
-        <v>385</v>
+        <v>369</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>121344</v>
+        <v>23711</v>
       </c>
       <c r="D22" t="n">
-        <v>2800</v>
+        <v>1248</v>
       </c>
       <c r="E22" t="n">
-        <v>316</v>
+        <v>181</v>
       </c>
       <c r="F22" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -938,10 +938,10 @@
         <v>2328</v>
       </c>
       <c r="E23" t="n">
-        <v>707</v>
+        <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>108</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">

--- a/output/roomself_excel/11375.xlsx
+++ b/output/roomself_excel/11375.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2704</v>
       </c>
-      <c r="E2" t="n">
-        <v>384</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>372</v>
+        <v>335</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>341</v>
+      </c>
+      <c r="J2" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3468</v>
       </c>
-      <c r="E3" t="n">
-        <v>529</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>418</v>
+        <v>381</v>
+      </c>
+      <c r="G3" t="n">
+        <v>43</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>457</v>
+      </c>
+      <c r="J3" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2776</v>
       </c>
-      <c r="E4" t="n">
-        <v>418</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>350</v>
+        <v>313</v>
+      </c>
+      <c r="G4" t="n">
+        <v>37</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>381</v>
+      </c>
+      <c r="J4" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +609,12 @@
       <c r="D5" t="n">
         <v>1132</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +631,12 @@
       <c r="D6" t="n">
         <v>1120</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +653,27 @@
       <c r="D7" t="n">
         <v>1792</v>
       </c>
-      <c r="E7" t="n">
-        <v>302</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>220</v>
+        <v>265</v>
+      </c>
+      <c r="G7" t="n">
+        <v>37</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>183</v>
+      </c>
+      <c r="J7" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +691,20 @@
       <c r="D8" t="n">
         <v>3988</v>
       </c>
-      <c r="E8" t="n">
-        <v>894</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>189</v>
       </c>
+      <c r="G8" t="n">
+        <v>43</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +721,20 @@
       <c r="D9" t="n">
         <v>4156</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>181</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>42</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +751,20 @@
       <c r="D10" t="n">
         <v>1128</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>124</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>37</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +781,27 @@
       <c r="D11" t="n">
         <v>2268</v>
       </c>
-      <c r="E11" t="n">
-        <v>415</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>228</v>
+        <v>380</v>
+      </c>
+      <c r="G11" t="n">
+        <v>42</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>184</v>
+      </c>
+      <c r="J11" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -695,11 +819,27 @@
       <c r="D12" t="n">
         <v>2180</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>358</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>42</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>187</v>
+      </c>
+      <c r="J12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +857,20 @@
       <c r="D13" t="n">
         <v>2028</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>209</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>37</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,10 +887,26 @@
       <c r="D14" t="n">
         <v>2020</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>130</v>
+      </c>
+      <c r="G14" t="n">
+        <v>17</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>375</v>
       </c>
-      <c r="F14" t="n">
+      <c r="J14" t="n">
         <v>18</v>
       </c>
     </row>
@@ -761,11 +925,27 @@
       <c r="D15" t="n">
         <v>3372</v>
       </c>
-      <c r="E15" t="n">
-        <v>696</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>385</v>
+        <v>353</v>
+      </c>
+      <c r="G15" t="n">
+        <v>35</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>490</v>
+      </c>
+      <c r="J15" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -783,10 +963,26 @@
       <c r="D16" t="n">
         <v>2800</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>316</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
+        <v>31</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>384</v>
+      </c>
+      <c r="J16" t="n">
         <v>31</v>
       </c>
     </row>
@@ -805,11 +1001,27 @@
       <c r="D17" t="n">
         <v>5012</v>
       </c>
-      <c r="E17" t="n">
-        <v>614</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>527</v>
+        <v>559</v>
+      </c>
+      <c r="G17" t="n">
+        <v>35</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>492</v>
+      </c>
+      <c r="J17" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="18">
@@ -827,12 +1039,20 @@
       <c r="D18" t="n">
         <v>2544</v>
       </c>
-      <c r="E18" t="n">
-        <v>432</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>212</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="G18" t="n">
+        <v>27</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1069,20 @@
       <c r="D19" t="n">
         <v>3080</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="G19" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1099,20 @@
       <c r="D20" t="n">
         <v>1432</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>175</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>37</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,11 +1129,27 @@
       <c r="D21" t="n">
         <v>3164</v>
       </c>
-      <c r="E21" t="n">
-        <v>433</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>369</v>
+        <v>351</v>
+      </c>
+      <c r="G21" t="n">
+        <v>27</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>388</v>
+      </c>
+      <c r="J21" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -915,12 +1167,20 @@
       <c r="D22" t="n">
         <v>1248</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>181</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>18</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1197,20 @@
       <c r="D23" t="n">
         <v>2328</v>
       </c>
-      <c r="E23" t="n">
-        <v>21</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="G23" t="n">
+        <v>31</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,11 +1227,27 @@
       <c r="D24" t="n">
         <v>2332</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>316</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>32</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>267</v>
+      </c>
+      <c r="J24" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11375.xlsx
+++ b/output/roomself_excel/11375.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,46 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -517,6 +557,26 @@
       <c r="J2" t="n">
         <v>37</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>179</v>
+      </c>
+      <c r="N2" t="n">
+        <v>37</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -555,6 +615,38 @@
       <c r="J3" t="n">
         <v>37</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>282</v>
+      </c>
+      <c r="N3" t="n">
+        <v>37</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>100</v>
+      </c>
+      <c r="R3" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -593,6 +685,26 @@
       <c r="J4" t="n">
         <v>37</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>184</v>
+      </c>
+      <c r="N4" t="n">
+        <v>37</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -615,6 +727,14 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -637,6 +757,14 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -675,6 +803,38 @@
       <c r="J7" t="n">
         <v>37</v>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>117</v>
+      </c>
+      <c r="N7" t="n">
+        <v>37</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>68</v>
+      </c>
+      <c r="R7" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -705,6 +865,14 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -735,6 +903,14 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -765,6 +941,26 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>94</v>
+      </c>
+      <c r="N10" t="n">
+        <v>37</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -803,6 +999,14 @@
       <c r="J11" t="n">
         <v>35</v>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -841,6 +1045,14 @@
       <c r="J12" t="n">
         <v>30</v>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -871,6 +1083,26 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>113</v>
+      </c>
+      <c r="N13" t="n">
+        <v>37</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -909,6 +1141,14 @@
       <c r="J14" t="n">
         <v>18</v>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -947,6 +1187,14 @@
       <c r="J15" t="n">
         <v>32</v>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -985,6 +1233,26 @@
       <c r="J16" t="n">
         <v>31</v>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>133</v>
+      </c>
+      <c r="N16" t="n">
+        <v>31</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1023,6 +1291,26 @@
       <c r="J17" t="n">
         <v>31</v>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>220</v>
+      </c>
+      <c r="N17" t="n">
+        <v>31</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1053,6 +1341,26 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>160</v>
+      </c>
+      <c r="N18" t="n">
+        <v>27</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1083,6 +1391,26 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>195</v>
+      </c>
+      <c r="N19" t="n">
+        <v>30</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1113,6 +1441,26 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>89</v>
+      </c>
+      <c r="N20" t="n">
+        <v>37</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1151,6 +1499,26 @@
       <c r="J21" t="n">
         <v>18</v>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>143</v>
+      </c>
+      <c r="N21" t="n">
+        <v>27</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1181,6 +1549,14 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1211,6 +1587,26 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1249,6 +1645,14 @@
       <c r="J24" t="n">
         <v>31</v>
       </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
